--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/ARKANSAS_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/ARKANSAS_2019.xlsx
@@ -2742,7 +2742,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C133">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C230">
@@ -10698,7 +10698,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C575">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C592">
@@ -13621,7 +13621,7 @@
         <v>63</v>
       </c>
       <c r="D737">
-        <v>0.009334716254259891</v>
+        <v>0.009334716254259893</v>
       </c>
     </row>
     <row r="738">
